--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T424"/>
+  <dimension ref="A1:T426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28412,6 +28412,138 @@
         <v>314.08</v>
       </c>
       <c r="T424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>281.18</v>
+      </c>
+      <c r="C425" t="n">
+        <v>263.44</v>
+      </c>
+      <c r="D425" t="n">
+        <v>254.95</v>
+      </c>
+      <c r="E425" t="n">
+        <v>252.68</v>
+      </c>
+      <c r="F425" t="n">
+        <v>257.59</v>
+      </c>
+      <c r="G425" t="n">
+        <v>261.09</v>
+      </c>
+      <c r="H425" t="n">
+        <v>256.02</v>
+      </c>
+      <c r="I425" t="n">
+        <v>251.51</v>
+      </c>
+      <c r="J425" t="n">
+        <v>265.23</v>
+      </c>
+      <c r="K425" t="n">
+        <v>284.66</v>
+      </c>
+      <c r="L425" t="n">
+        <v>314.68</v>
+      </c>
+      <c r="M425" t="n">
+        <v>304.02</v>
+      </c>
+      <c r="N425" t="n">
+        <v>297.83</v>
+      </c>
+      <c r="O425" t="n">
+        <v>308.32</v>
+      </c>
+      <c r="P425" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>304.4</v>
+      </c>
+      <c r="R425" t="n">
+        <v>311.37</v>
+      </c>
+      <c r="S425" t="n">
+        <v>313.76</v>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>279.55</v>
+      </c>
+      <c r="C426" t="n">
+        <v>261.92</v>
+      </c>
+      <c r="D426" t="n">
+        <v>251.78</v>
+      </c>
+      <c r="E426" t="n">
+        <v>249.96</v>
+      </c>
+      <c r="F426" t="n">
+        <v>255.56</v>
+      </c>
+      <c r="G426" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="H426" t="n">
+        <v>254.31</v>
+      </c>
+      <c r="I426" t="n">
+        <v>250.37</v>
+      </c>
+      <c r="J426" t="n">
+        <v>264.61</v>
+      </c>
+      <c r="K426" t="n">
+        <v>284.03</v>
+      </c>
+      <c r="L426" t="n">
+        <v>313</v>
+      </c>
+      <c r="M426" t="n">
+        <v>302.07</v>
+      </c>
+      <c r="N426" t="n">
+        <v>296.47</v>
+      </c>
+      <c r="O426" t="n">
+        <v>306.96</v>
+      </c>
+      <c r="P426" t="n">
+        <v>310.48</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>303.95</v>
+      </c>
+      <c r="R426" t="n">
+        <v>310.56</v>
+      </c>
+      <c r="S426" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="T426" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28428,7 +28560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B425"/>
+  <dimension ref="A1:B427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32681,6 +32813,26 @@
       </c>
       <c r="B425" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -32849,28 +33001,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2961177091472136</v>
+        <v>-0.2974464182793513</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04220082668620817</v>
+        <v>0.04305054459258328</v>
       </c>
       <c r="M2" t="n">
-        <v>8.318995329746082</v>
+        <v>8.285999276656201</v>
       </c>
       <c r="N2" t="n">
-        <v>112.9305304341088</v>
+        <v>112.4055577374417</v>
       </c>
       <c r="O2" t="n">
-        <v>10.62687773685709</v>
+        <v>10.60214873209397</v>
       </c>
       <c r="P2" t="n">
-        <v>289.6888799049301</v>
+        <v>289.7025004813962</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32927,28 +33079,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3774269023935194</v>
+        <v>-0.3757626493156055</v>
       </c>
       <c r="J3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0922155759449601</v>
+        <v>0.09246130566317068</v>
       </c>
       <c r="M3" t="n">
-        <v>7.033537888682804</v>
+        <v>7.007760425383976</v>
       </c>
       <c r="N3" t="n">
-        <v>79.57437865611844</v>
+        <v>79.21224004648548</v>
       </c>
       <c r="O3" t="n">
-        <v>8.920447222876129</v>
+        <v>8.900125844418463</v>
       </c>
       <c r="P3" t="n">
-        <v>271.1833693386487</v>
+        <v>271.1663168525239</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33005,28 +33157,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2152393575823401</v>
+        <v>-0.2159463604727007</v>
       </c>
       <c r="J4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03883896096532946</v>
+        <v>0.0395292569321789</v>
       </c>
       <c r="M4" t="n">
-        <v>6.618341557937462</v>
+        <v>6.59485441888554</v>
       </c>
       <c r="N4" t="n">
-        <v>64.71063601869284</v>
+        <v>64.419577357295</v>
       </c>
       <c r="O4" t="n">
-        <v>8.044292139069343</v>
+        <v>8.026180745366689</v>
       </c>
       <c r="P4" t="n">
-        <v>259.8839979737564</v>
+        <v>259.891258088831</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33083,28 +33235,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2592320140212328</v>
+        <v>-0.2633000305750654</v>
       </c>
       <c r="J5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05518942561024709</v>
+        <v>0.05740757575269406</v>
       </c>
       <c r="M5" t="n">
-        <v>6.573458650479388</v>
+        <v>6.562044408898732</v>
       </c>
       <c r="N5" t="n">
-        <v>65.38705831907994</v>
+        <v>65.16676270033254</v>
       </c>
       <c r="O5" t="n">
-        <v>8.086226457321112</v>
+        <v>8.072593307006896</v>
       </c>
       <c r="P5" t="n">
-        <v>262.4332313964696</v>
+        <v>262.474750969389</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33161,28 +33313,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1230504714697241</v>
+        <v>-0.1261685394217666</v>
       </c>
       <c r="J6" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L6" t="n">
-        <v>0.014635237515915</v>
+        <v>0.01554292594472528</v>
       </c>
       <c r="M6" t="n">
-        <v>6.070482939504807</v>
+        <v>6.058129299184436</v>
       </c>
       <c r="N6" t="n">
-        <v>58.32726515752636</v>
+        <v>58.10234275441159</v>
       </c>
       <c r="O6" t="n">
-        <v>7.637228892571334</v>
+        <v>7.622489275454022</v>
       </c>
       <c r="P6" t="n">
-        <v>263.0582623753978</v>
+        <v>263.0900148204692</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33239,28 +33391,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02435664739214102</v>
+        <v>0.02238713539600556</v>
       </c>
       <c r="J7" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K7" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005425074263221141</v>
+        <v>0.00046371146513835</v>
       </c>
       <c r="M7" t="n">
-        <v>6.437553502720976</v>
+        <v>6.416670160487279</v>
       </c>
       <c r="N7" t="n">
-        <v>62.25464355969218</v>
+        <v>61.9814396738686</v>
       </c>
       <c r="O7" t="n">
-        <v>7.890161187180664</v>
+        <v>7.872829203905582</v>
       </c>
       <c r="P7" t="n">
-        <v>261.786469295474</v>
+        <v>261.8065561523842</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33317,28 +33469,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05586107385836443</v>
+        <v>0.05406052986703177</v>
       </c>
       <c r="J8" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K8" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004155487848335526</v>
+        <v>0.003937839252429187</v>
       </c>
       <c r="M8" t="n">
-        <v>5.331123147227419</v>
+        <v>5.314230085116848</v>
       </c>
       <c r="N8" t="n">
-        <v>42.50242781939174</v>
+        <v>42.32126544519905</v>
       </c>
       <c r="O8" t="n">
-        <v>6.519388607790744</v>
+        <v>6.505479647589334</v>
       </c>
       <c r="P8" t="n">
-        <v>255.481765293632</v>
+        <v>255.5001433483002</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33395,28 +33547,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08652935185181314</v>
+        <v>0.08479775610035581</v>
       </c>
       <c r="J9" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K9" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01509018667411699</v>
+        <v>0.01466455130811883</v>
       </c>
       <c r="M9" t="n">
-        <v>4.390360799550359</v>
+        <v>4.376822287375772</v>
       </c>
       <c r="N9" t="n">
-        <v>27.77502215090953</v>
+        <v>27.6600931880336</v>
       </c>
       <c r="O9" t="n">
-        <v>5.270201338744995</v>
+        <v>5.259286376309395</v>
       </c>
       <c r="P9" t="n">
-        <v>250.3611303703797</v>
+        <v>250.3788035827036</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33473,28 +33625,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09406311369300203</v>
+        <v>0.09312892181023574</v>
       </c>
       <c r="J10" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K10" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02056598364445017</v>
+        <v>0.02040147236909995</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9767347487639</v>
+        <v>3.962768010217635</v>
       </c>
       <c r="N10" t="n">
-        <v>23.94914751087891</v>
+        <v>23.84104858335822</v>
       </c>
       <c r="O10" t="n">
-        <v>4.893786622941269</v>
+        <v>4.882729624232558</v>
       </c>
       <c r="P10" t="n">
-        <v>263.3286576084131</v>
+        <v>263.338192281612</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33551,28 +33703,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0354245756406428</v>
+        <v>0.03662525427012431</v>
       </c>
       <c r="J11" t="n">
+        <v>425</v>
+      </c>
+      <c r="K11" t="n">
         <v>423</v>
       </c>
-      <c r="K11" t="n">
-        <v>421</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.00298982033065609</v>
+        <v>0.003232529814513718</v>
       </c>
       <c r="M11" t="n">
-        <v>3.69522976805588</v>
+        <v>3.682560197654629</v>
       </c>
       <c r="N11" t="n">
-        <v>23.88909069028561</v>
+        <v>23.78351650913975</v>
       </c>
       <c r="O11" t="n">
-        <v>4.887646743606335</v>
+        <v>4.876834681341961</v>
       </c>
       <c r="P11" t="n">
-        <v>282.1701631294953</v>
+        <v>282.1579296482389</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33629,28 +33781,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01992166649751272</v>
+        <v>0.02149135009478714</v>
       </c>
       <c r="J12" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K12" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0008594059144820809</v>
+        <v>0.00101146349717518</v>
       </c>
       <c r="M12" t="n">
-        <v>3.923741821872003</v>
+        <v>3.91181560081495</v>
       </c>
       <c r="N12" t="n">
-        <v>26.22438168593537</v>
+        <v>26.11603722334365</v>
       </c>
       <c r="O12" t="n">
-        <v>5.120974681243344</v>
+        <v>5.110385232381572</v>
       </c>
       <c r="P12" t="n">
-        <v>311.7079470162537</v>
+        <v>311.6919321507485</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33707,28 +33859,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.05321931249547768</v>
+        <v>-0.05021401914453289</v>
       </c>
       <c r="J13" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K13" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006229383413850487</v>
+        <v>0.005605510014549453</v>
       </c>
       <c r="M13" t="n">
-        <v>3.901522630448735</v>
+        <v>3.896182568336537</v>
       </c>
       <c r="N13" t="n">
-        <v>25.68060609730979</v>
+        <v>25.60726138734154</v>
       </c>
       <c r="O13" t="n">
-        <v>5.067603585257019</v>
+        <v>5.060361784234556</v>
       </c>
       <c r="P13" t="n">
-        <v>301.4327113504068</v>
+        <v>301.4020468047034</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33785,28 +33937,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1462816268931473</v>
+        <v>-0.1430351236632737</v>
       </c>
       <c r="J14" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K14" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05656485650477128</v>
+        <v>0.05469886976276161</v>
       </c>
       <c r="M14" t="n">
-        <v>3.656057062588316</v>
+        <v>3.652812756035845</v>
       </c>
       <c r="N14" t="n">
-        <v>20.28479317818402</v>
+        <v>20.24169173633354</v>
       </c>
       <c r="O14" t="n">
-        <v>4.503864249528845</v>
+        <v>4.499076764885607</v>
       </c>
       <c r="P14" t="n">
-        <v>297.8010654010363</v>
+        <v>297.7679380517918</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33863,28 +34015,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.274204175921864</v>
+        <v>-0.26797891062086</v>
       </c>
       <c r="J15" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K15" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1917097471286903</v>
+        <v>0.1849325729102193</v>
       </c>
       <c r="M15" t="n">
-        <v>3.290988368875268</v>
+        <v>3.300894078831834</v>
       </c>
       <c r="N15" t="n">
-        <v>18.0571567804247</v>
+        <v>18.15913829190261</v>
       </c>
       <c r="O15" t="n">
-        <v>4.249371339436541</v>
+        <v>4.26135404442093</v>
       </c>
       <c r="P15" t="n">
-        <v>308.7230289685828</v>
+        <v>308.6595497577549</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33941,28 +34093,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3714863780050494</v>
+        <v>-0.3666299800804062</v>
       </c>
       <c r="J16" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K16" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3080328716634252</v>
+        <v>0.3036263781791591</v>
       </c>
       <c r="M16" t="n">
-        <v>3.340595681826664</v>
+        <v>3.346638352848745</v>
       </c>
       <c r="N16" t="n">
-        <v>17.65843773672437</v>
+        <v>17.68775194675739</v>
       </c>
       <c r="O16" t="n">
-        <v>4.20219439539919</v>
+        <v>4.205680913568859</v>
       </c>
       <c r="P16" t="n">
-        <v>315.486270073185</v>
+        <v>315.4367465774484</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34019,28 +34171,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.369906246139607</v>
+        <v>-0.3665580309049996</v>
       </c>
       <c r="J17" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K17" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3006971117868871</v>
+        <v>0.2987656380650027</v>
       </c>
       <c r="M17" t="n">
-        <v>3.439563201409619</v>
+        <v>3.436683531514014</v>
       </c>
       <c r="N17" t="n">
-        <v>18.08610530145473</v>
+        <v>18.05458919251235</v>
       </c>
       <c r="O17" t="n">
-        <v>4.252776187557338</v>
+        <v>4.249069214841334</v>
       </c>
       <c r="P17" t="n">
-        <v>310.7541701678673</v>
+        <v>310.7200028881404</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34097,28 +34249,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2936583173037217</v>
+        <v>-0.2927623066447418</v>
       </c>
       <c r="J18" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K18" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2477841693663151</v>
+        <v>0.2488171402449153</v>
       </c>
       <c r="M18" t="n">
-        <v>2.964455968759361</v>
+        <v>2.9546957592355</v>
       </c>
       <c r="N18" t="n">
-        <v>14.87918641188375</v>
+        <v>14.81375939635897</v>
       </c>
       <c r="O18" t="n">
-        <v>3.857354846508647</v>
+        <v>3.848864689276433</v>
       </c>
       <c r="P18" t="n">
-        <v>317.9764490456755</v>
+        <v>317.9673070750567</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34175,28 +34327,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2536122617173663</v>
+        <v>-0.2530816740967323</v>
       </c>
       <c r="J19" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K19" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2505499200959285</v>
+        <v>0.2519880606785873</v>
       </c>
       <c r="M19" t="n">
-        <v>2.578852484368301</v>
+        <v>2.569075704412032</v>
       </c>
       <c r="N19" t="n">
-        <v>10.93489447190512</v>
+        <v>10.88477743832494</v>
       </c>
       <c r="O19" t="n">
-        <v>3.306795196546819</v>
+        <v>3.299208607882342</v>
       </c>
       <c r="P19" t="n">
-        <v>320.0472116707876</v>
+        <v>320.0417971429367</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34234,7 +34386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T424"/>
+  <dimension ref="A1:T426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77417,6 +77569,210 @@
         </is>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-38.528343820073104,178.28912201068303</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-38.52863091631393,178.28826933910548</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-38.528983394484314,178.2874820488697</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-38.52937983729952,178.28673872299487</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-38.529827031389814,178.28604614696425</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-38.53029998893632,178.28528650243697</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-38.53084498707763,178.2844785867312</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-38.53145077748655,178.28384229053543</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-38.532086292606564,178.28344059909168</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-38.53275057014134,178.28309302387274</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-38.53354037214722,178.28279053274866</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-38.53429882587209,178.28247099381255</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>-38.53498844067757,178.28224974661197</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-38.53568724046551,178.28222013034258</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>-38.536368641131446,178.28206944157733</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-38.53704128117969,178.28181067814907</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>-38.537738608045764,178.2816956751081</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>-38.538428596931894,178.28152909627426</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-38.528332298202464,178.28911048943246</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-38.52862017193063,178.28825859539722</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-38.528960986674626,178.28745964261782</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-38.52936061032054,178.28671949744268</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-38.52981268178475,178.28603179846235</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-38.530291369081546,178.28527662917867</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-38.530835296097905,178.28446339836916</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-38.531445034331,178.28383148679475</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-38.53208316912703,178.2834347233255</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-38.53274739627696,178.28308705328342</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-38.53353489126072,178.2827726185622</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-38.53429640628393,178.28244889224368</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-38.534986857276486,178.2822343141397</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-38.53568548119266,178.28220472862438</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>-38.536368913255444,178.28207147215824</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>-38.537040560838555,178.28180561060788</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>-38.53773731143272,178.2816865534441</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>-38.5384285489091,178.28152875843156</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T426"/>
+  <dimension ref="A1:T428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28544,6 +28544,138 @@
         <v>313.73</v>
       </c>
       <c r="T426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>279.55</v>
+      </c>
+      <c r="C427" t="n">
+        <v>260.11</v>
+      </c>
+      <c r="D427" t="n">
+        <v>251.08</v>
+      </c>
+      <c r="E427" t="n">
+        <v>249.37</v>
+      </c>
+      <c r="F427" t="n">
+        <v>255.12</v>
+      </c>
+      <c r="G427" t="n">
+        <v>259.22</v>
+      </c>
+      <c r="H427" t="n">
+        <v>253.82</v>
+      </c>
+      <c r="I427" t="n">
+        <v>249.71</v>
+      </c>
+      <c r="J427" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="K427" t="n">
+        <v>284.01</v>
+      </c>
+      <c r="L427" t="n">
+        <v>312.65</v>
+      </c>
+      <c r="M427" t="n">
+        <v>301.64</v>
+      </c>
+      <c r="N427" t="n">
+        <v>295.88</v>
+      </c>
+      <c r="O427" t="n">
+        <v>306.32</v>
+      </c>
+      <c r="P427" t="n">
+        <v>309.94</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>303.53</v>
+      </c>
+      <c r="R427" t="n">
+        <v>310.06</v>
+      </c>
+      <c r="S427" t="n">
+        <v>313.26</v>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>276.51</v>
+      </c>
+      <c r="C428" t="n">
+        <v>259.74</v>
+      </c>
+      <c r="D428" t="n">
+        <v>250.93</v>
+      </c>
+      <c r="E428" t="n">
+        <v>249</v>
+      </c>
+      <c r="F428" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="G428" t="n">
+        <v>258.76</v>
+      </c>
+      <c r="H428" t="n">
+        <v>253.62</v>
+      </c>
+      <c r="I428" t="n">
+        <v>249.46</v>
+      </c>
+      <c r="J428" t="n">
+        <v>264.35</v>
+      </c>
+      <c r="K428" t="n">
+        <v>284.06</v>
+      </c>
+      <c r="L428" t="n">
+        <v>312.55</v>
+      </c>
+      <c r="M428" t="n">
+        <v>301.51</v>
+      </c>
+      <c r="N428" t="n">
+        <v>295.53</v>
+      </c>
+      <c r="O428" t="n">
+        <v>305.83</v>
+      </c>
+      <c r="P428" t="n">
+        <v>309.64</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>303.24</v>
+      </c>
+      <c r="R428" t="n">
+        <v>309.86</v>
+      </c>
+      <c r="S428" t="n">
+        <v>312.92</v>
+      </c>
+      <c r="T428" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28560,7 +28692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B427"/>
+  <dimension ref="A1:B429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32833,6 +32965,26 @@
       </c>
       <c r="B427" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>
@@ -33001,28 +33153,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2974464182793513</v>
+        <v>-0.3010128772196768</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K2" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04305054459258328</v>
+        <v>0.04451547179421267</v>
       </c>
       <c r="M2" t="n">
-        <v>8.285999276656201</v>
+        <v>8.264317215065969</v>
       </c>
       <c r="N2" t="n">
-        <v>112.4055577374417</v>
+        <v>111.9465775512725</v>
       </c>
       <c r="O2" t="n">
-        <v>10.60214873209397</v>
+        <v>10.58048096975145</v>
       </c>
       <c r="P2" t="n">
-        <v>289.7025004813962</v>
+        <v>289.7391197027089</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33079,28 +33231,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3757626493156055</v>
+        <v>-0.3768271098550183</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K3" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09246130566317068</v>
+        <v>0.0939308955672129</v>
       </c>
       <c r="M3" t="n">
-        <v>7.007760425383976</v>
+        <v>6.979893089774624</v>
       </c>
       <c r="N3" t="n">
-        <v>79.21224004648548</v>
+        <v>78.84336111485499</v>
       </c>
       <c r="O3" t="n">
-        <v>8.900125844418463</v>
+        <v>8.879378419397103</v>
       </c>
       <c r="P3" t="n">
-        <v>271.1663168525239</v>
+        <v>271.1772452042651</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33157,28 +33309,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2159463604727007</v>
+        <v>-0.2189390392933515</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K4" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0395292569321789</v>
+        <v>0.04102441456382477</v>
       </c>
       <c r="M4" t="n">
-        <v>6.59485441888554</v>
+        <v>6.579092811202099</v>
       </c>
       <c r="N4" t="n">
-        <v>64.419577357295</v>
+        <v>64.16025574657729</v>
       </c>
       <c r="O4" t="n">
-        <v>8.026180745366689</v>
+        <v>8.010009722002669</v>
       </c>
       <c r="P4" t="n">
-        <v>259.891258088831</v>
+        <v>259.9220127594118</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33235,28 +33387,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2633000305750654</v>
+        <v>-0.2693138164811918</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K5" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05740757575269406</v>
+        <v>0.06041444310397237</v>
       </c>
       <c r="M5" t="n">
-        <v>6.562044408898732</v>
+        <v>6.559937088626893</v>
       </c>
       <c r="N5" t="n">
-        <v>65.16676270033254</v>
+        <v>65.0374944216904</v>
       </c>
       <c r="O5" t="n">
-        <v>8.072593307006896</v>
+        <v>8.064582718386017</v>
       </c>
       <c r="P5" t="n">
-        <v>262.474750969389</v>
+        <v>262.5362262909111</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33313,28 +33465,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1261685394217666</v>
+        <v>-0.1307147596511673</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K6" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01554292594472528</v>
+        <v>0.01682914376038791</v>
       </c>
       <c r="M6" t="n">
-        <v>6.058129299184436</v>
+        <v>6.05330040656617</v>
       </c>
       <c r="N6" t="n">
-        <v>58.10234275441159</v>
+        <v>57.9296565182606</v>
       </c>
       <c r="O6" t="n">
-        <v>7.622489275454022</v>
+        <v>7.611153428900288</v>
       </c>
       <c r="P6" t="n">
-        <v>263.0900148204692</v>
+        <v>263.1363843880097</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33391,28 +33543,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02238713539600556</v>
+        <v>0.01906028476175929</v>
       </c>
       <c r="J7" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K7" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00046371146513835</v>
+        <v>0.0003398591421187591</v>
       </c>
       <c r="M7" t="n">
-        <v>6.416670160487279</v>
+        <v>6.402586273693212</v>
       </c>
       <c r="N7" t="n">
-        <v>61.9814396738686</v>
+        <v>61.74465041907798</v>
       </c>
       <c r="O7" t="n">
-        <v>7.872829203905582</v>
+        <v>7.857776429695488</v>
       </c>
       <c r="P7" t="n">
-        <v>261.8065561523842</v>
+        <v>261.8405406295365</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33469,28 +33621,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05406052986703177</v>
+        <v>0.05090715303657533</v>
       </c>
       <c r="J8" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K8" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003937839252429187</v>
+        <v>0.003530646468743903</v>
       </c>
       <c r="M8" t="n">
-        <v>5.314230085116848</v>
+        <v>5.303680411950337</v>
       </c>
       <c r="N8" t="n">
-        <v>42.32126544519905</v>
+        <v>42.17142833065889</v>
       </c>
       <c r="O8" t="n">
-        <v>6.505479647589334</v>
+        <v>6.493953212848003</v>
       </c>
       <c r="P8" t="n">
-        <v>255.5001433483002</v>
+        <v>255.5323784632644</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33547,28 +33699,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08479775610035581</v>
+        <v>0.08179568082067834</v>
       </c>
       <c r="J9" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K9" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01466455130811883</v>
+        <v>0.01379659097390207</v>
       </c>
       <c r="M9" t="n">
-        <v>4.376822287375772</v>
+        <v>4.368567105272176</v>
       </c>
       <c r="N9" t="n">
-        <v>27.6600931880336</v>
+        <v>27.57442282295015</v>
       </c>
       <c r="O9" t="n">
-        <v>5.259286376309395</v>
+        <v>5.251135384176469</v>
       </c>
       <c r="P9" t="n">
-        <v>250.3788035827036</v>
+        <v>250.4094921493928</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33625,28 +33777,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09312892181023574</v>
+        <v>0.09170617709556865</v>
       </c>
       <c r="J10" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K10" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02040147236909995</v>
+        <v>0.02001704749198097</v>
       </c>
       <c r="M10" t="n">
-        <v>3.962768010217635</v>
+        <v>3.951380987380323</v>
       </c>
       <c r="N10" t="n">
-        <v>23.84104858335822</v>
+        <v>23.73923161552175</v>
       </c>
       <c r="O10" t="n">
-        <v>4.882729624232558</v>
+        <v>4.872292234207811</v>
       </c>
       <c r="P10" t="n">
-        <v>263.338192281612</v>
+        <v>263.3527361675791</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33703,28 +33855,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03662525427012431</v>
+        <v>0.03748738892797385</v>
       </c>
       <c r="J11" t="n">
+        <v>427</v>
+      </c>
+      <c r="K11" t="n">
         <v>425</v>
       </c>
-      <c r="K11" t="n">
-        <v>423</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.003232529814513718</v>
+        <v>0.003425425934534765</v>
       </c>
       <c r="M11" t="n">
-        <v>3.682560197654629</v>
+        <v>3.668646006952302</v>
       </c>
       <c r="N11" t="n">
-        <v>23.78351650913975</v>
+        <v>23.67523111807446</v>
       </c>
       <c r="O11" t="n">
-        <v>4.876834681341961</v>
+        <v>4.865719999966547</v>
       </c>
       <c r="P11" t="n">
-        <v>282.1579296482389</v>
+        <v>282.1491293694509</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33781,28 +33933,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02149135009478714</v>
+        <v>0.02181137433232568</v>
       </c>
       <c r="J12" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K12" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00101146349717518</v>
+        <v>0.001054100898415511</v>
       </c>
       <c r="M12" t="n">
-        <v>3.91181560081495</v>
+        <v>3.894822981747263</v>
       </c>
       <c r="N12" t="n">
-        <v>26.11603722334365</v>
+        <v>25.99422205593135</v>
       </c>
       <c r="O12" t="n">
-        <v>5.110385232381572</v>
+        <v>5.098452908082152</v>
       </c>
       <c r="P12" t="n">
-        <v>311.6919321507485</v>
+        <v>311.6886609754425</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33859,28 +34011,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.05021401914453289</v>
+        <v>-0.04872211208484976</v>
       </c>
       <c r="J13" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K13" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005605510014549453</v>
+        <v>0.005339115823788987</v>
       </c>
       <c r="M13" t="n">
-        <v>3.896182568336537</v>
+        <v>3.884421027046357</v>
       </c>
       <c r="N13" t="n">
-        <v>25.60726138734154</v>
+        <v>25.49816265559425</v>
       </c>
       <c r="O13" t="n">
-        <v>5.060361784234556</v>
+        <v>5.049570541698992</v>
       </c>
       <c r="P13" t="n">
-        <v>301.4020468047034</v>
+        <v>301.38679640496</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33937,28 +34089,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1430351236632737</v>
+        <v>-0.1412800182427446</v>
       </c>
       <c r="J14" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K14" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05469886976276161</v>
+        <v>0.05399718633001838</v>
       </c>
       <c r="M14" t="n">
-        <v>3.652812756035845</v>
+        <v>3.643185201993377</v>
       </c>
       <c r="N14" t="n">
-        <v>20.24169173633354</v>
+        <v>20.16200692430109</v>
       </c>
       <c r="O14" t="n">
-        <v>4.499076764885607</v>
+        <v>4.490212347350745</v>
       </c>
       <c r="P14" t="n">
-        <v>297.7679380517918</v>
+        <v>297.7499976426898</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34015,28 +34167,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.26797891062086</v>
+        <v>-0.2634509420331304</v>
       </c>
       <c r="J15" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K15" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1849325729102193</v>
+        <v>0.1807742996734029</v>
       </c>
       <c r="M15" t="n">
-        <v>3.300894078831834</v>
+        <v>3.304053777342022</v>
       </c>
       <c r="N15" t="n">
-        <v>18.15913829190261</v>
+        <v>18.17412621289999</v>
       </c>
       <c r="O15" t="n">
-        <v>4.26135404442093</v>
+        <v>4.263112268390311</v>
       </c>
       <c r="P15" t="n">
-        <v>308.6595497577549</v>
+        <v>308.6132980059575</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34093,28 +34245,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3666299800804062</v>
+        <v>-0.3624836182042132</v>
       </c>
       <c r="J16" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K16" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3036263781791591</v>
+        <v>0.3003126799904443</v>
       </c>
       <c r="M16" t="n">
-        <v>3.346638352848745</v>
+        <v>3.349624512146038</v>
       </c>
       <c r="N16" t="n">
-        <v>17.68775194675739</v>
+        <v>17.68863212049489</v>
       </c>
       <c r="O16" t="n">
-        <v>4.205680913568859</v>
+        <v>4.205785553317583</v>
       </c>
       <c r="P16" t="n">
-        <v>315.4367465774484</v>
+        <v>315.3943924846956</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34171,28 +34323,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3665580309049996</v>
+        <v>-0.3640570512990114</v>
       </c>
       <c r="J17" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K17" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2987656380650027</v>
+        <v>0.2980122332800831</v>
       </c>
       <c r="M17" t="n">
-        <v>3.436683531514014</v>
+        <v>3.430724690957692</v>
       </c>
       <c r="N17" t="n">
-        <v>18.05458919251235</v>
+        <v>18.00053127934423</v>
       </c>
       <c r="O17" t="n">
-        <v>4.249069214841334</v>
+        <v>4.242703298528454</v>
       </c>
       <c r="P17" t="n">
-        <v>310.7200028881404</v>
+        <v>310.6944378056563</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34249,28 +34401,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2927623066447418</v>
+        <v>-0.2928574570686948</v>
       </c>
       <c r="J18" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K18" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2488171402449153</v>
+        <v>0.2511483679872779</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9546957592355</v>
+        <v>2.941326506649439</v>
       </c>
       <c r="N18" t="n">
-        <v>14.81375939635897</v>
+        <v>14.74446338735063</v>
       </c>
       <c r="O18" t="n">
-        <v>3.848864689276433</v>
+        <v>3.839852000709225</v>
       </c>
       <c r="P18" t="n">
-        <v>317.9673070750567</v>
+        <v>317.9682801497199</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34327,28 +34479,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2530816740967323</v>
+        <v>-0.2531910904747636</v>
       </c>
       <c r="J19" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K19" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2519880606785873</v>
+        <v>0.2543774605092499</v>
       </c>
       <c r="M19" t="n">
-        <v>2.569075704412032</v>
+        <v>2.557863540521034</v>
       </c>
       <c r="N19" t="n">
-        <v>10.88477743832494</v>
+        <v>10.83398465534425</v>
       </c>
       <c r="O19" t="n">
-        <v>3.299208607882342</v>
+        <v>3.291501884450964</v>
       </c>
       <c r="P19" t="n">
-        <v>320.0417971429367</v>
+        <v>320.0429163447477</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34386,7 +34538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T426"/>
+  <dimension ref="A1:T428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77773,6 +77925,210 @@
         </is>
       </c>
     </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-38.528332298202464,178.28911048943246</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-38.5286073776305,178.2882458019068</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-38.52895603857713,178.28745469486697</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-38.529356439762076,178.28671532719562</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-38.52980957152521,178.28602868844297</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-38.530287493487606,178.28527219004008</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-38.53083251915009,178.28445904614918</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-38.531441709345685,178.28382523199826</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-38.53208231268904,178.28343311222844</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-38.53274729551936,178.28308686374092</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-38.533533749408996,178.28276888644035</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-38.53429587273314,178.28244401856452</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>-38.5349861703592,178.28222761917027</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-38.53568465329884,178.2821974807572</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-38.53636809688335,178.2820653804156</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-38.53703988851997,178.2818008809028</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>-38.53773651105393,178.28168092278744</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>-38.5384277965517,178.28152346556288</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-38.52831080955651,178.28908900195688</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-38.528604762220866,178.28824318666346</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-38.52895497827048,178.28745363463474</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-38.52935382432702,178.28671271195617</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-38.52980801639542,178.2860271334334</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-38.53028441974053,178.2852686693443</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-38.53083138570194,178.28445726973297</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-38.53144044988145,178.28382286275732</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-38.532081859280666,178.28343225929467</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-38.532747547413365,178.2830873375972</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-38.53353342316561,178.28276782011983</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-38.534295711427035,178.28244254512663</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-38.53498576286569,178.28222364757826</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-38.535684019442286,178.28219193160893</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-38.53636764334316,178.28206199611415</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-38.53703942429988,178.2817976151541</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-38.537736190902336,178.28167867052483</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>-38.53842725229302,178.28151963667918</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0262/nzd0262.xlsx
+++ b/data/nzd0262/nzd0262.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T428"/>
+  <dimension ref="A1:T430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28678,6 +28678,138 @@
       <c r="T428" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>274.68</v>
+      </c>
+      <c r="C429" t="n">
+        <v>258.07</v>
+      </c>
+      <c r="D429" t="n">
+        <v>248.96</v>
+      </c>
+      <c r="E429" t="n">
+        <v>247.39</v>
+      </c>
+      <c r="F429" t="n">
+        <v>252.65</v>
+      </c>
+      <c r="G429" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="H429" t="n">
+        <v>252.22</v>
+      </c>
+      <c r="I429" t="n">
+        <v>248.71</v>
+      </c>
+      <c r="J429" t="n">
+        <v>263.79</v>
+      </c>
+      <c r="K429" t="n">
+        <v>283.54</v>
+      </c>
+      <c r="L429" t="n">
+        <v>312.74</v>
+      </c>
+      <c r="M429" t="n">
+        <v>300.53</v>
+      </c>
+      <c r="N429" t="n">
+        <v>294.17</v>
+      </c>
+      <c r="O429" t="n">
+        <v>302.03</v>
+      </c>
+      <c r="P429" t="n">
+        <v>306.98</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="R429" t="n">
+        <v>309.86</v>
+      </c>
+      <c r="S429" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:53:54+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>270.4</v>
+      </c>
+      <c r="C430" t="n">
+        <v>256.47</v>
+      </c>
+      <c r="D430" t="n">
+        <v>247.77</v>
+      </c>
+      <c r="E430" t="n">
+        <v>245.83</v>
+      </c>
+      <c r="F430" t="n">
+        <v>250.76</v>
+      </c>
+      <c r="G430" t="n">
+        <v>255.67</v>
+      </c>
+      <c r="H430" t="n">
+        <v>250</v>
+      </c>
+      <c r="I430" t="n">
+        <v>248.06</v>
+      </c>
+      <c r="J430" t="n">
+        <v>262.28</v>
+      </c>
+      <c r="K430" t="n">
+        <v>280.73</v>
+      </c>
+      <c r="L430" t="n">
+        <v>310.36</v>
+      </c>
+      <c r="M430" t="n">
+        <v>297.67</v>
+      </c>
+      <c r="N430" t="n">
+        <v>291.54</v>
+      </c>
+      <c r="O430" t="n">
+        <v>299.95</v>
+      </c>
+      <c r="P430" t="n">
+        <v>306.19</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>300.98</v>
+      </c>
+      <c r="R430" t="n">
+        <v>310.33</v>
+      </c>
+      <c r="S430" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28692,7 +28824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B429"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32985,6 +33117,26 @@
       </c>
       <c r="B429" t="n">
         <v>-0.02</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -33153,28 +33305,28 @@
         <v>0.0581</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3010128772196768</v>
+        <v>-0.3097954216872828</v>
       </c>
       <c r="J2" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04451547179421267</v>
+        <v>0.04739449001460361</v>
       </c>
       <c r="M2" t="n">
-        <v>8.264317215065969</v>
+        <v>8.267958631541505</v>
       </c>
       <c r="N2" t="n">
-        <v>111.9465775512725</v>
+        <v>111.8192563456116</v>
       </c>
       <c r="O2" t="n">
-        <v>10.58048096975145</v>
+        <v>10.57446246130798</v>
       </c>
       <c r="P2" t="n">
-        <v>289.7391197027089</v>
+        <v>289.8296457076433</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33231,28 +33383,28 @@
         <v>0.0659</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3768271098550183</v>
+        <v>-0.3804112479654874</v>
       </c>
       <c r="J3" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K3" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0939308955672129</v>
+        <v>0.0965015470692232</v>
       </c>
       <c r="M3" t="n">
-        <v>6.979893089774624</v>
+        <v>6.964649641697367</v>
       </c>
       <c r="N3" t="n">
-        <v>78.84336111485499</v>
+        <v>78.53824838516483</v>
       </c>
       <c r="O3" t="n">
-        <v>8.879378419397103</v>
+        <v>8.862180791721913</v>
       </c>
       <c r="P3" t="n">
-        <v>271.1772452042651</v>
+        <v>271.2141879935187</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33309,28 +33461,28 @@
         <v>0.0659</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2189390392933515</v>
+        <v>-0.2244011400504245</v>
       </c>
       <c r="J4" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04102441456382477</v>
+        <v>0.04339952623291921</v>
       </c>
       <c r="M4" t="n">
-        <v>6.579092811202099</v>
+        <v>6.575739668538611</v>
       </c>
       <c r="N4" t="n">
-        <v>64.16025574657729</v>
+        <v>64.00727306656289</v>
       </c>
       <c r="O4" t="n">
-        <v>8.010009722002669</v>
+        <v>8.000454553746486</v>
       </c>
       <c r="P4" t="n">
-        <v>259.9220127594118</v>
+        <v>259.978363393874</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33387,28 +33539,28 @@
         <v>0.0418</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2693138164811918</v>
+        <v>-0.2776433459321808</v>
       </c>
       <c r="J5" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06041444310397237</v>
+        <v>0.06435292344383647</v>
       </c>
       <c r="M5" t="n">
-        <v>6.559937088626893</v>
+        <v>6.56927719299228</v>
       </c>
       <c r="N5" t="n">
-        <v>65.0374944216904</v>
+        <v>65.07826664062311</v>
       </c>
       <c r="O5" t="n">
-        <v>8.064582718386017</v>
+        <v>8.067110179030848</v>
       </c>
       <c r="P5" t="n">
-        <v>262.5362262909111</v>
+        <v>262.6217064864753</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33465,28 +33617,28 @@
         <v>0.0461</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1307147596511673</v>
+        <v>-0.1383281382213595</v>
       </c>
       <c r="J6" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01682914376038791</v>
+        <v>0.01893212647931986</v>
       </c>
       <c r="M6" t="n">
-        <v>6.05330040656617</v>
+        <v>6.064312684452061</v>
       </c>
       <c r="N6" t="n">
-        <v>57.9296565182606</v>
+        <v>57.94927721740201</v>
       </c>
       <c r="O6" t="n">
-        <v>7.611153428900288</v>
+        <v>7.612442263649821</v>
       </c>
       <c r="P6" t="n">
-        <v>263.1363843880097</v>
+        <v>263.2143464919646</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33543,28 +33695,28 @@
         <v>0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01906028476175929</v>
+        <v>0.01353441107032316</v>
       </c>
       <c r="J7" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K7" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003398591421187591</v>
+        <v>0.0001729780450876461</v>
       </c>
       <c r="M7" t="n">
-        <v>6.402586273693212</v>
+        <v>6.399124690896162</v>
       </c>
       <c r="N7" t="n">
-        <v>61.74465041907798</v>
+        <v>61.61101211313976</v>
       </c>
       <c r="O7" t="n">
-        <v>7.857776429695488</v>
+        <v>7.849268253355835</v>
       </c>
       <c r="P7" t="n">
-        <v>261.8405406295365</v>
+        <v>261.8972126888581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33621,28 +33773,28 @@
         <v>0.0409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05090715303657533</v>
+        <v>0.04530144364836203</v>
       </c>
       <c r="J8" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K8" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003530646468743903</v>
+        <v>0.002820148606698325</v>
       </c>
       <c r="M8" t="n">
-        <v>5.303680411950337</v>
+        <v>5.305050669835525</v>
       </c>
       <c r="N8" t="n">
-        <v>42.17142833065889</v>
+        <v>42.13502336257545</v>
       </c>
       <c r="O8" t="n">
-        <v>6.493953212848003</v>
+        <v>6.491149617947151</v>
       </c>
       <c r="P8" t="n">
-        <v>255.5323784632644</v>
+        <v>255.5899109751483</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33699,28 +33851,28 @@
         <v>0.0463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08179568082067834</v>
+        <v>0.07769890477165617</v>
       </c>
       <c r="J9" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K9" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01379659097390207</v>
+        <v>0.0125737004019969</v>
       </c>
       <c r="M9" t="n">
-        <v>4.368567105272176</v>
+        <v>4.364684455185498</v>
       </c>
       <c r="N9" t="n">
-        <v>27.57442282295015</v>
+        <v>27.5289109119899</v>
       </c>
       <c r="O9" t="n">
-        <v>5.251135384176469</v>
+        <v>5.246800064038071</v>
       </c>
       <c r="P9" t="n">
-        <v>250.4094921493928</v>
+        <v>250.451534079811</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33777,28 +33929,28 @@
         <v>0.0549</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09170617709556865</v>
+        <v>0.08899602256861543</v>
       </c>
       <c r="J10" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K10" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02001704749198097</v>
+        <v>0.01906126662127439</v>
       </c>
       <c r="M10" t="n">
-        <v>3.951380987380323</v>
+        <v>3.94645295380213</v>
       </c>
       <c r="N10" t="n">
-        <v>23.73923161552175</v>
+        <v>23.66731418987004</v>
       </c>
       <c r="O10" t="n">
-        <v>4.872292234207811</v>
+        <v>4.864906390658513</v>
       </c>
       <c r="P10" t="n">
-        <v>263.3527361675791</v>
+        <v>263.3805528877961</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33855,28 +34007,28 @@
         <v>0.0653</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03748738892797385</v>
+        <v>0.03648971534525014</v>
       </c>
       <c r="J11" t="n">
+        <v>429</v>
+      </c>
+      <c r="K11" t="n">
         <v>427</v>
       </c>
-      <c r="K11" t="n">
-        <v>425</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.003425425934534765</v>
+        <v>0.00328227585762475</v>
       </c>
       <c r="M11" t="n">
-        <v>3.668646006952302</v>
+        <v>3.658936593111874</v>
       </c>
       <c r="N11" t="n">
-        <v>23.67523111807446</v>
+        <v>23.57855459450276</v>
       </c>
       <c r="O11" t="n">
-        <v>4.865719999966547</v>
+        <v>4.855775385507732</v>
       </c>
       <c r="P11" t="n">
-        <v>282.1491293694509</v>
+        <v>282.1593644688292</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33933,28 +34085,28 @@
         <v>0.0585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02181137433232568</v>
+        <v>0.02110593558237384</v>
       </c>
       <c r="J12" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K12" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001054100898415511</v>
+        <v>0.000998375908516036</v>
       </c>
       <c r="M12" t="n">
-        <v>3.894822981747263</v>
+        <v>3.882671524382592</v>
       </c>
       <c r="N12" t="n">
-        <v>25.99422205593135</v>
+        <v>25.88206789398254</v>
       </c>
       <c r="O12" t="n">
-        <v>5.098452908082152</v>
+        <v>5.08744217598417</v>
       </c>
       <c r="P12" t="n">
-        <v>311.6886609754425</v>
+        <v>311.6959099514237</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34011,28 +34163,28 @@
         <v>0.0737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04872211208484976</v>
+        <v>-0.04965969406619947</v>
       </c>
       <c r="J13" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K13" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005339115823788987</v>
+        <v>0.005607480204069093</v>
       </c>
       <c r="M13" t="n">
-        <v>3.884421027046357</v>
+        <v>3.873402954161945</v>
       </c>
       <c r="N13" t="n">
-        <v>25.49816265559425</v>
+        <v>25.39310643226065</v>
       </c>
       <c r="O13" t="n">
-        <v>5.049570541698992</v>
+        <v>5.03915731370441</v>
       </c>
       <c r="P13" t="n">
-        <v>301.38679640496</v>
+        <v>301.3964295533413</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34089,28 +34241,28 @@
         <v>0.0718</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1412800182427446</v>
+        <v>-0.1423106116836778</v>
       </c>
       <c r="J14" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K14" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05399718633001838</v>
+        <v>0.05532044215472787</v>
       </c>
       <c r="M14" t="n">
-        <v>3.643185201993377</v>
+        <v>3.632889604575262</v>
       </c>
       <c r="N14" t="n">
-        <v>20.16200692430109</v>
+        <v>20.08126649705157</v>
       </c>
       <c r="O14" t="n">
-        <v>4.490212347350745</v>
+        <v>4.48121261457784</v>
       </c>
       <c r="P14" t="n">
-        <v>297.7499976426898</v>
+        <v>297.7605842596135</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34167,28 +34319,28 @@
         <v>0.066</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2634509420331304</v>
+        <v>-0.2639163798039788</v>
       </c>
       <c r="J15" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K15" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1807742996734029</v>
+        <v>0.1829950106890122</v>
       </c>
       <c r="M15" t="n">
-        <v>3.304053777342022</v>
+        <v>3.293748031564051</v>
       </c>
       <c r="N15" t="n">
-        <v>18.17412621289999</v>
+        <v>18.09522061429449</v>
       </c>
       <c r="O15" t="n">
-        <v>4.263112268390311</v>
+        <v>4.253847742255767</v>
       </c>
       <c r="P15" t="n">
-        <v>308.6132980059575</v>
+        <v>308.6180795067753</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34245,28 +34397,28 @@
         <v>0.0624</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3624836182042132</v>
+        <v>-0.3615011253806248</v>
       </c>
       <c r="J16" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K16" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3003126799904443</v>
+        <v>0.3015724618339043</v>
       </c>
       <c r="M16" t="n">
-        <v>3.349624512146038</v>
+        <v>3.338350023309852</v>
       </c>
       <c r="N16" t="n">
-        <v>17.68863212049489</v>
+        <v>17.61143372393394</v>
       </c>
       <c r="O16" t="n">
-        <v>4.205785553317583</v>
+        <v>4.196597874937977</v>
       </c>
       <c r="P16" t="n">
-        <v>315.3943924846956</v>
+        <v>315.384321001563</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34323,28 +34475,28 @@
         <v>0.0727</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3640570512990114</v>
+        <v>-0.3631696481305715</v>
       </c>
       <c r="J17" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K17" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2980122332800831</v>
+        <v>0.2993716322132267</v>
       </c>
       <c r="M17" t="n">
-        <v>3.430724690957692</v>
+        <v>3.418325042581969</v>
       </c>
       <c r="N17" t="n">
-        <v>18.00053127934423</v>
+        <v>17.92312842804378</v>
       </c>
       <c r="O17" t="n">
-        <v>4.242703298528454</v>
+        <v>4.233571592407973</v>
       </c>
       <c r="P17" t="n">
-        <v>310.6944378056563</v>
+        <v>310.685338076544</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34401,28 +34553,28 @@
         <v>0.0486</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2928574570686948</v>
+        <v>-0.2927914116153176</v>
       </c>
       <c r="J18" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K18" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2511483679872779</v>
+        <v>0.2532727166500529</v>
       </c>
       <c r="M18" t="n">
-        <v>2.941326506649439</v>
+        <v>2.928712781461164</v>
       </c>
       <c r="N18" t="n">
-        <v>14.74446338735063</v>
+        <v>14.67600772750565</v>
       </c>
       <c r="O18" t="n">
-        <v>3.839852000709225</v>
+        <v>3.830927789388055</v>
       </c>
       <c r="P18" t="n">
-        <v>317.9682801497199</v>
+        <v>317.9676004103</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34479,28 +34631,28 @@
         <v>0.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2531910904747636</v>
+        <v>-0.2541006887199973</v>
       </c>
       <c r="J19" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K19" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2543774605092499</v>
+        <v>0.257906381472691</v>
       </c>
       <c r="M19" t="n">
-        <v>2.557863540521034</v>
+        <v>2.550550397300632</v>
       </c>
       <c r="N19" t="n">
-        <v>10.83398465534425</v>
+        <v>10.78762763270186</v>
       </c>
       <c r="O19" t="n">
-        <v>3.291501884450964</v>
+        <v>3.284452409870154</v>
       </c>
       <c r="P19" t="n">
-        <v>320.0429163447477</v>
+        <v>320.0522513396719</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34538,7 +34690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T428"/>
+  <dimension ref="A1:T430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78129,6 +78281,210 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-38.52829787395474,178.28907606706835</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-38.528592957533235,178.2882313827298</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-38.52894105290883,178.28743971025435</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-38.52934244364927,178.2867013321328</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-38.529792111657365,178.28601122993035</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-38.5302766685517,178.2852597910693</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-38.53082345156405,178.284444834821</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-38.531436671488436,178.283815755035</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-38.53207903807294,178.28342695215164</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-38.53274492771555,178.2830824094921</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-38.533534043028006,178.2827698461288</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-38.53429449542664,178.28243143767205</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-38.53498417946108,178.28220821510675</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-38.535679103811034,178.28214889740033</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-38.536363621949,178.28203198864287</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-38.53703823973782,178.28178928186446</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-38.537736190902336,178.28167867052483</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>-38.53842637187425,178.28151344289682</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:53:54+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-38.52826762019068,178.28904581499793</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-38.52858164765149,178.28822007357553</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-38.528932641141125,178.28743129908307</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-38.529331416407416,178.2866903057236</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-38.52977875167533,178.28599787099333</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-38.53026377217538,178.2852450194609</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-38.53081087028513,178.284425116609</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-38.53143339688075,178.28380959500953</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-38.532071430886454,178.28341264182157</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-38.532730771267495,178.28305577877632</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-38.5335262784331,178.28274446770274</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-38.53429094668458,178.2823990220407</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-38.53498111743003,178.28217837143148</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-38.5356764131428,178.2821253418353</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-38.53636242762365,178.28202307664998</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-38.5370358065814,178.28177216483775</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>-38.5377369432585,178.281683963342</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>-38.53842593966856,178.28151040231282</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
